--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -32346,13 +32346,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O157" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R157" t="n">
-        <v>0.2717880746444645</v>
+        <v>0.2754608864639843</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -32505,10 +32505,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O158" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2365</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -26779,7 +26779,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -32597,7 +32597,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -38022,13 +38022,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="O186" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="R186" t="n">
-        <v>0.08814748366847497</v>
+        <v>0.1799677791564697</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -38181,10 +38181,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="O187" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -44310,12 +44310,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -44340,104 +44340,102 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>0.00367281181951979</v>
+        <v>0</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_C_NEW</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_NEW</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
         </is>
       </c>
       <c r="AT218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44469,12 +44467,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -44499,38 +44497,41 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_NEW</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_C_NEW</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>Hepatitis C (newly acquired)</t>
+          <t>Acute Viral Hepatitis C</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
@@ -44540,12 +44541,12 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
@@ -44555,7 +44556,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -44570,7 +44571,7 @@
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG219" t="inlineStr">
@@ -44590,12 +44591,12 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Newly acquired hepatitis C, separate from unspecified hepatitis C.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -44608,70 +44609,1114 @@
       </c>
       <c r="AO219" t="inlineStr">
         <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="n">
+        <v>1</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_NEW</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="AP219" t="inlineStr">
+      <c r="AP220" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ219" t="inlineStr">
+      <c r="AQ220" t="inlineStr">
         <is>
           <t>legacy_gap_fill</t>
         </is>
       </c>
-      <c r="AS219" t="inlineStr">
+      <c r="AS220" t="inlineStr">
         <is>
           <t>SER_AU_HEPATITIS_C_NEW</t>
         </is>
       </c>
-      <c r="AT219" t="n">
+      <c r="AT220" t="n">
         <v>1</v>
       </c>
-      <c r="AU219" t="inlineStr">
+      <c r="AU220" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV219" t="inlineStr">
+      <c r="AV220" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW219" t="inlineStr">
+      <c r="AW220" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX219" t="inlineStr">
+      <c r="AX220" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY219" t="inlineStr">
+      <c r="AY220" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ219" t="inlineStr">
+      <c r="AZ220" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA219" t="inlineStr">
+      <c r="BA220" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB219" t="inlineStr">
+      <c r="BB220" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC219" t="inlineStr">
+      <c r="BC220" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="n">
+        <v>1</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_NEW</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_NEW</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Hepatitis C (newly acquired)</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Newly acquired hepatitis C, separate from unspecified hepatitis C.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_NEW</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>36</v>
+      </c>
+      <c r="O222" t="n">
+        <v>36</v>
+      </c>
+      <c r="P222" t="n">
+        <v>36</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.01031413727796979</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>36</v>
+      </c>
+      <c r="O223" t="n">
+        <v>36</v>
+      </c>
+      <c r="P223" t="n">
+        <v>36</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>10</v>
+      </c>
+      <c r="O224" t="n">
+        <v>10</v>
+      </c>
+      <c r="P224" t="n">
+        <v>10</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44708,7 +45753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -44791,7 +45836,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -44801,7 +45846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -44821,7 +45866,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
@@ -44853,7 +45898,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2366</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -38022,13 +38022,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O186" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R186" t="n">
-        <v>0.1799677791564697</v>
+        <v>0.1873134027955093</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -38181,10 +38181,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O187" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2427</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -32346,13 +32346,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O157" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="R157" t="n">
-        <v>0.2754608864639843</v>
+        <v>0.2938249455615832</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -32505,10 +32505,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O158" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -38022,13 +38022,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O186" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R186" t="n">
-        <v>0.1873134027955093</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -38181,10 +38181,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O187" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -42259,16 +42259,16 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -42416,13 +42416,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
@@ -45715,6 +45715,1051 @@
         </is>
       </c>
       <c r="BC224" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>29</v>
+      </c>
+      <c r="O227" t="n">
+        <v>29</v>
+      </c>
+      <c r="P227" t="n">
+        <v>29</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.008308610585031217</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>29</v>
+      </c>
+      <c r="O228" t="n">
+        <v>29</v>
+      </c>
+      <c r="P228" t="n">
+        <v>29</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>9</v>
+      </c>
+      <c r="O229" t="n">
+        <v>9</v>
+      </c>
+      <c r="P229" t="n">
+        <v>9</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -45753,7 +46798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -45836,7 +46881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -45846,7 +46891,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -45866,7 +46911,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -45898,7 +46943,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2429</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -32346,13 +32346,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="O157" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="R157" t="n">
-        <v>0.2938249455615832</v>
+        <v>0.3232074401177416</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -32505,10 +32505,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="O158" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2466</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -28418,7 +28418,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -28660,7 +28660,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29705,7 +29705,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -30750,7 +30750,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31553,7 +31553,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -32346,13 +32346,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="O157" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="R157" t="n">
-        <v>0.3232074401177416</v>
+        <v>0.3415714992153405</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -32505,10 +32505,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="O158" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -33690,7 +33690,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34336,7 +34336,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35139,7 +35139,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -35381,7 +35381,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -36184,7 +36184,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -37229,7 +37229,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -37471,7 +37471,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -38022,13 +38022,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O186" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="R186" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.2056774618931082</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -38181,10 +38181,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O187" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -39366,7 +39366,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -39770,7 +39770,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40815,7 +40815,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -41860,7 +41860,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -42102,7 +42102,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42905,7 +42905,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43147,7 +43147,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -43950,7 +43950,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -44192,7 +44192,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44984,7 +44984,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45388,7 +45388,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45630,7 +45630,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -45787,16 +45787,16 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -45944,13 +45944,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -46675,7 +46675,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46760,6 +46760,1051 @@
         </is>
       </c>
       <c r="BC229" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>40</v>
+      </c>
+      <c r="O232" t="n">
+        <v>40</v>
+      </c>
+      <c r="P232" t="n">
+        <v>40</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.01146015253107754</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>40</v>
+      </c>
+      <c r="O233" t="n">
+        <v>40</v>
+      </c>
+      <c r="P233" t="n">
+        <v>40</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>5</v>
+      </c>
+      <c r="O234" t="n">
+        <v>5</v>
+      </c>
+      <c r="P234" t="n">
+        <v>5</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -46798,7 +47843,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -46881,7 +47926,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -46891,7 +47936,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -46911,7 +47956,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -46943,7 +47988,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2474</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -44743,13 +44743,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="O220" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="R220" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.1358940373222322</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -44902,10 +44902,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="O221" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -47805,6 +47805,1051 @@
         </is>
       </c>
       <c r="BC234" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>31</v>
+      </c>
+      <c r="O237" t="n">
+        <v>31</v>
+      </c>
+      <c r="P237" t="n">
+        <v>31</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.008881618211585096</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>31</v>
+      </c>
+      <c r="O238" t="n">
+        <v>31</v>
+      </c>
+      <c r="P238" t="n">
+        <v>31</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA238" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>9</v>
+      </c>
+      <c r="O239" t="n">
+        <v>9</v>
+      </c>
+      <c r="P239" t="n">
+        <v>9</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -47843,7 +48888,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -47926,7 +48971,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -47936,7 +48981,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -47956,7 +49001,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -47988,7 +49033,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2523</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -44743,13 +44743,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O220" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="R220" t="n">
-        <v>0.1358940373222322</v>
+        <v>0.1505852846003114</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -44902,10 +44902,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O221" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2590</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -52879,13 +52879,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O264" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R264" t="n">
-        <v>0.2130230855321478</v>
+        <v>0.2166958973516676</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -53038,10 +53038,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O265" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -60819,13 +60819,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="O304" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="R304" t="n">
-        <v>0.1909862146150291</v>
+        <v>0.2203687091711874</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -60978,10 +60978,10 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="O305" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="U305" t="inlineStr">
         <is>
@@ -67584,6 +67584,1051 @@
         </is>
       </c>
       <c r="BC337" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N338" t="n">
+        <v>0</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0</v>
+      </c>
+      <c r="P338" t="n">
+        <v>0</v>
+      </c>
+      <c r="R338" t="n">
+        <v>0</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO338" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP338" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ338" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS338" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT338" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU338" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV338" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW338" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX338" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY338" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA338" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB338" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC338" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>0</v>
+      </c>
+      <c r="O339" t="n">
+        <v>0</v>
+      </c>
+      <c r="P339" t="n">
+        <v>0</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis C</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ339" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK339" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM339" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN339" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO339" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP339" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ339" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS339" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_C; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT339" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU339" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV339" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW339" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX339" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY339" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA339" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB339" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC339" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>34</v>
+      </c>
+      <c r="O340" t="n">
+        <v>34</v>
+      </c>
+      <c r="P340" t="n">
+        <v>34</v>
+      </c>
+      <c r="R340" t="n">
+        <v>0.00974112965141591</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO340" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP340" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ340" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR340" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS340" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT340" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV340" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW340" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY340" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA340" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB340" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC340" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>34</v>
+      </c>
+      <c r="O341" t="n">
+        <v>34</v>
+      </c>
+      <c r="P341" t="n">
+        <v>34</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF341" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ341" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK341" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM341" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN341" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO341" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP341" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ341" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR341" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS341" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT341" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV341" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW341" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX341" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY341" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA341" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB341" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC341" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>6</v>
+      </c>
+      <c r="O342" t="n">
+        <v>6</v>
+      </c>
+      <c r="P342" t="n">
+        <v>6</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ342" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK342" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM342" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN342" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO342" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP342" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ342" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR342" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS342" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT342" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU342" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV342" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW342" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX342" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY342" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA342" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB342" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC342" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -67622,7 +68667,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -67705,7 +68750,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -67715,7 +68760,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -67735,7 +68780,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -67767,7 +68812,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3159</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -52879,13 +52879,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O264" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R264" t="n">
-        <v>0.2166958973516676</v>
+        <v>0.2203687091711874</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -53038,10 +53038,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O265" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -60819,13 +60819,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O304" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R304" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.2240415209907072</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -60978,10 +60978,10 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O305" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U305" t="inlineStr">
         <is>
@@ -68812,7 +68812,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3202</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -52879,13 +52879,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O264" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R264" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.2240415209907072</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -53038,10 +53038,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O265" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -60819,13 +60819,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O304" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="R304" t="n">
-        <v>0.2240415209907072</v>
+        <v>0.246078391907826</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -60978,10 +60978,10 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O305" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="U305" t="inlineStr">
         <is>
@@ -68812,7 +68812,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3204</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -68634,6 +68634,657 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N343" t="n">
+        <v>27</v>
+      </c>
+      <c r="O343" t="n">
+        <v>27</v>
+      </c>
+      <c r="P343" t="n">
+        <v>27</v>
+      </c>
+      <c r="R343" t="n">
+        <v>0.007735602958477341</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO343" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP343" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ343" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR343" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS343" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT343" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU343" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV343" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW343" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX343" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY343" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA343" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB343" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC343" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>27</v>
+      </c>
+      <c r="O344" t="n">
+        <v>27</v>
+      </c>
+      <c r="P344" t="n">
+        <v>27</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF344" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ344" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK344" t="inlineStr">
+        <is>
+          <t>Confirmed acute hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM344" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN344" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO344" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP344" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ344" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR344" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS344" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT344" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV344" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW344" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX344" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY344" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA344" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB344" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC344" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>5</v>
+      </c>
+      <c r="O345" t="n">
+        <v>5</v>
+      </c>
+      <c r="P345" t="n">
+        <v>5</v>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>Hepatitis C, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF345" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ345" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK345" t="inlineStr">
+        <is>
+          <t>Probable acute hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM345" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO345" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP345" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ345" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR345" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS345" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT345" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV345" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW345" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX345" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY345" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA345" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB345" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC345" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -68667,7 +69318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -68750,7 +69401,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -68760,7 +69411,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -68780,7 +69431,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -68812,7 +69463,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3211</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -2184,14 +2184,12 @@
       <c r="O12" t="n">
         <v>2</v>
       </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
       <c r="R12" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2204,23 +2202,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2481,14 +2469,12 @@
       <c r="O14" t="n">
         <v>39</v>
       </c>
+      <c r="P14" t="n">
+        <v>39</v>
+      </c>
       <c r="R14" t="n">
         <v>0.0111736487178006</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2501,23 +2487,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2778,14 +2754,12 @@
       <c r="O16" t="n">
         <v>37</v>
       </c>
+      <c r="P16" t="n">
+        <v>37</v>
+      </c>
       <c r="R16" t="n">
         <v>0.01060064109124673</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2798,23 +2772,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3075,14 +3039,12 @@
       <c r="O18" t="n">
         <v>43</v>
       </c>
+      <c r="P18" t="n">
+        <v>43</v>
+      </c>
       <c r="R18" t="n">
         <v>0.01231966397090836</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3095,23 +3057,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3372,14 +3324,12 @@
       <c r="O20" t="n">
         <v>27</v>
       </c>
+      <c r="P20" t="n">
+        <v>27</v>
+      </c>
       <c r="R20" t="n">
         <v>0.007735602958477341</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3392,23 +3342,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5088,14 +5028,12 @@
       <c r="O32" t="n">
         <v>61</v>
       </c>
+      <c r="P32" t="n">
+        <v>61</v>
+      </c>
       <c r="R32" t="n">
         <v>0.01747673260989325</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5108,23 +5046,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5385,14 +5313,12 @@
       <c r="O34" t="n">
         <v>37</v>
       </c>
+      <c r="P34" t="n">
+        <v>37</v>
+      </c>
       <c r="R34" t="n">
         <v>0.01060064109124673</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5405,23 +5331,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5682,14 +5598,12 @@
       <c r="O36" t="n">
         <v>31</v>
       </c>
+      <c r="P36" t="n">
+        <v>31</v>
+      </c>
       <c r="R36" t="n">
         <v>0.008881618211585096</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5702,23 +5616,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5979,14 +5883,12 @@
       <c r="O38" t="n">
         <v>36</v>
       </c>
+      <c r="P38" t="n">
+        <v>36</v>
+      </c>
       <c r="R38" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5999,23 +5901,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7677,14 +7569,12 @@
       <c r="O50" t="n">
         <v>34</v>
       </c>
+      <c r="P50" t="n">
+        <v>34</v>
+      </c>
       <c r="R50" t="n">
         <v>0.00974112965141591</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7697,23 +7587,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7974,14 +7854,12 @@
       <c r="O52" t="n">
         <v>45</v>
       </c>
+      <c r="P52" t="n">
+        <v>45</v>
+      </c>
       <c r="R52" t="n">
         <v>0.01289267159746223</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7994,23 +7872,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8271,14 +8139,12 @@
       <c r="O54" t="n">
         <v>39</v>
       </c>
+      <c r="P54" t="n">
+        <v>39</v>
+      </c>
       <c r="R54" t="n">
         <v>0.0111736487178006</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8291,23 +8157,13 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8568,14 +8424,12 @@
       <c r="O56" t="n">
         <v>43</v>
       </c>
+      <c r="P56" t="n">
+        <v>43</v>
+      </c>
       <c r="R56" t="n">
         <v>0.01231966397090836</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8588,23 +8442,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10269,14 +10113,12 @@
       <c r="O68" t="n">
         <v>53</v>
       </c>
+      <c r="P68" t="n">
+        <v>53</v>
+      </c>
       <c r="R68" t="n">
         <v>0.01518470210367774</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10289,23 +10131,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10566,14 +10398,12 @@
       <c r="O70" t="n">
         <v>39</v>
       </c>
+      <c r="P70" t="n">
+        <v>39</v>
+      </c>
       <c r="R70" t="n">
         <v>0.0111736487178006</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10586,23 +10416,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10863,14 +10683,12 @@
       <c r="O72" t="n">
         <v>37</v>
       </c>
+      <c r="P72" t="n">
+        <v>37</v>
+      </c>
       <c r="R72" t="n">
         <v>0.01060064109124673</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10883,23 +10701,13 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -11160,14 +10968,12 @@
       <c r="O74" t="n">
         <v>34</v>
       </c>
+      <c r="P74" t="n">
+        <v>34</v>
+      </c>
       <c r="R74" t="n">
         <v>0.00974112965141591</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11180,23 +10986,13 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12879,14 +12675,12 @@
       <c r="O86" t="n">
         <v>40</v>
       </c>
+      <c r="P86" t="n">
+        <v>40</v>
+      </c>
       <c r="R86" t="n">
         <v>0.01146015253107754</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12899,23 +12693,13 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
       </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV86" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13176,14 +12960,12 @@
       <c r="O88" t="n">
         <v>40</v>
       </c>
+      <c r="P88" t="n">
+        <v>40</v>
+      </c>
       <c r="R88" t="n">
         <v>0.01146015253107754</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13196,23 +12978,13 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13473,14 +13245,12 @@
       <c r="O90" t="n">
         <v>33</v>
       </c>
+      <c r="P90" t="n">
+        <v>33</v>
+      </c>
       <c r="R90" t="n">
         <v>0.009454625838138971</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13493,23 +13263,13 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV90" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13770,14 +13530,12 @@
       <c r="O92" t="n">
         <v>16</v>
       </c>
+      <c r="P92" t="n">
+        <v>16</v>
+      </c>
       <c r="R92" t="n">
         <v>0.004584061012431017</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13790,23 +13548,13 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
       </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV92" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14067,14 +13815,12 @@
       <c r="O94" t="n">
         <v>14</v>
       </c>
+      <c r="P94" t="n">
+        <v>14</v>
+      </c>
       <c r="R94" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14087,23 +13833,13 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
       </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV94" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15786,14 +15522,12 @@
       <c r="O106" t="n">
         <v>32</v>
       </c>
+      <c r="P106" t="n">
+        <v>32</v>
+      </c>
       <c r="R106" t="n">
         <v>0.009168122024862033</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15806,23 +15540,13 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16083,14 +15807,12 @@
       <c r="O108" t="n">
         <v>21</v>
       </c>
+      <c r="P108" t="n">
+        <v>21</v>
+      </c>
       <c r="R108" t="n">
         <v>0.006016580078815709</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16103,23 +15825,13 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
       </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV108" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16380,14 +16092,12 @@
       <c r="O110" t="n">
         <v>36</v>
       </c>
+      <c r="P110" t="n">
+        <v>36</v>
+      </c>
       <c r="R110" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16400,23 +16110,13 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
       </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV110" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16677,14 +16377,12 @@
       <c r="O112" t="n">
         <v>35</v>
       </c>
+      <c r="P112" t="n">
+        <v>35</v>
+      </c>
       <c r="R112" t="n">
         <v>0.01002763346469285</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16697,23 +16395,13 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -18378,14 +18066,12 @@
       <c r="O124" t="n">
         <v>33</v>
       </c>
+      <c r="P124" t="n">
+        <v>33</v>
+      </c>
       <c r="R124" t="n">
         <v>0.009454625838138971</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18398,23 +18084,13 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
       </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV124" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -18675,14 +18351,12 @@
       <c r="O126" t="n">
         <v>20</v>
       </c>
+      <c r="P126" t="n">
+        <v>20</v>
+      </c>
       <c r="R126" t="n">
         <v>0.00573007626553877</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18695,23 +18369,13 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
       </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV126" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -18972,14 +18636,12 @@
       <c r="O128" t="n">
         <v>36</v>
       </c>
+      <c r="P128" t="n">
+        <v>36</v>
+      </c>
       <c r="R128" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18992,23 +18654,13 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
       </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV128" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -19269,14 +18921,12 @@
       <c r="O130" t="n">
         <v>34</v>
       </c>
+      <c r="P130" t="n">
+        <v>34</v>
+      </c>
       <c r="R130" t="n">
         <v>0.00974112965141591</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19289,23 +18939,13 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
       </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV130" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -20961,14 +20601,12 @@
       <c r="O142" t="n">
         <v>43</v>
       </c>
+      <c r="P142" t="n">
+        <v>43</v>
+      </c>
       <c r="R142" t="n">
         <v>0.01231966397090836</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20981,23 +20619,13 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
       </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV142" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21258,14 +20886,12 @@
       <c r="O144" t="n">
         <v>38</v>
       </c>
+      <c r="P144" t="n">
+        <v>38</v>
+      </c>
       <c r="R144" t="n">
         <v>0.01088714490452366</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21278,23 +20904,13 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
       </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV144" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21555,14 +21171,12 @@
       <c r="O146" t="n">
         <v>36</v>
       </c>
+      <c r="P146" t="n">
+        <v>36</v>
+      </c>
       <c r="R146" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21575,23 +21189,13 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
       </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV146" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21852,14 +21456,12 @@
       <c r="O148" t="n">
         <v>29</v>
       </c>
+      <c r="P148" t="n">
+        <v>29</v>
+      </c>
       <c r="R148" t="n">
         <v>0.008308610585031217</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21872,23 +21474,13 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
       </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV148" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -22149,14 +21741,12 @@
       <c r="O150" t="n">
         <v>38</v>
       </c>
+      <c r="P150" t="n">
+        <v>38</v>
+      </c>
       <c r="R150" t="n">
         <v>0.01088714490452366</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22169,23 +21759,13 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
       </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV150" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -23724,14 +23304,12 @@
       <c r="O161" t="n">
         <v>36</v>
       </c>
+      <c r="P161" t="n">
+        <v>36</v>
+      </c>
       <c r="R161" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23744,23 +23322,13 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
       </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV161" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24021,14 +23589,12 @@
       <c r="O163" t="n">
         <v>29</v>
       </c>
+      <c r="P163" t="n">
+        <v>29</v>
+      </c>
       <c r="R163" t="n">
         <v>0.008308610585031217</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24041,23 +23607,13 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
       </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV163" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24318,14 +23874,12 @@
       <c r="O165" t="n">
         <v>40</v>
       </c>
+      <c r="P165" t="n">
+        <v>40</v>
+      </c>
       <c r="R165" t="n">
         <v>0.01146015253107754</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24338,23 +23892,13 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
       </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV165" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24615,14 +24159,12 @@
       <c r="O167" t="n">
         <v>31</v>
       </c>
+      <c r="P167" t="n">
+        <v>31</v>
+      </c>
       <c r="R167" t="n">
         <v>0.008881618211585096</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24635,23 +24177,13 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
       </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV167" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24912,14 +24444,12 @@
       <c r="O169" t="n">
         <v>34</v>
       </c>
+      <c r="P169" t="n">
+        <v>34</v>
+      </c>
       <c r="R169" t="n">
         <v>0.00974112965141591</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24932,23 +24462,13 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
       </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV169" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -25209,14 +24729,12 @@
       <c r="O171" t="n">
         <v>27</v>
       </c>
+      <c r="P171" t="n">
+        <v>27</v>
+      </c>
       <c r="R171" t="n">
         <v>0.007735602958477341</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25229,23 +24747,13 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
       </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV171" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -25282,6 +24790,291 @@
         </is>
       </c>
       <c r="BC171" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>36</v>
+      </c>
+      <c r="O173" t="n">
+        <v>36</v>
+      </c>
+      <c r="P173" t="n">
+        <v>36</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.01031413727796979</v>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -25320,7 +25113,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25196,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -25413,7 +25206,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -25465,7 +25258,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3244</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d210/2026-2029.xlsx
+++ b/diseases/d210/2026-2029.xlsx
@@ -19201,13 +19201,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O132" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R132" t="n">
-        <v>0.2350599564492666</v>
+        <v>0.246078391907826</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -22021,13 +22021,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O152" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="R152" t="n">
-        <v>0.2534240155468655</v>
+        <v>0.2607696391859051</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -24400,12 +24400,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -24439,25 +24439,27 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="O169" t="n">
-        <v>34</v>
-      </c>
-      <c r="P169" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R169" t="n">
-        <v>0.00974112965141591</v>
+        <v>0.1065115427660739</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_NEW</t>
+        </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
@@ -24465,48 +24467,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS169" t="inlineStr"/>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_AU_HEPATITIS_C_NEW</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24538,12 +24544,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -24568,7 +24574,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -24577,83 +24583,74 @@
         </is>
       </c>
       <c r="N170" t="n">
+        <v>34</v>
+      </c>
+      <c r="O170" t="n">
+        <v>34</v>
+      </c>
+      <c r="P170" t="n">
+        <v>34</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.00974112965141591</v>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
         <v>0</v>
       </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP170" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
-        </is>
-      </c>
-      <c r="AT170" t="n">
-        <v>1</v>
-      </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24685,12 +24682,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -24715,7 +24712,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -24724,16 +24721,21 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P171" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>0.007735602958477341</v>
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
@@ -24742,7 +24744,7 @@
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
@@ -24750,48 +24752,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS171" t="inlineStr"/>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -24823,12 +24829,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -24853,7 +24859,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -24862,83 +24868,74 @@
         </is>
       </c>
       <c r="N172" t="n">
+        <v>27</v>
+      </c>
+      <c r="O172" t="n">
+        <v>27</v>
+      </c>
+      <c r="P172" t="n">
+        <v>27</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.007735602958477341</v>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
         <v>0</v>
       </c>
-      <c r="O172" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" t="n">
-        <v>0</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0</v>
-      </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
-        </is>
-      </c>
-      <c r="AT172" t="n">
-        <v>1</v>
-      </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24970,111 +24967,258 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>D210</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Acute hepatitis C</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
         <is>
           <t>急性丙型肝炎</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N173" t="n">
+      <c r="N174" t="n">
         <v>36</v>
       </c>
-      <c r="O173" t="n">
+      <c r="O174" t="n">
         <v>36</v>
       </c>
-      <c r="P173" t="n">
+      <c r="P174" t="n">
         <v>36</v>
       </c>
-      <c r="R173" t="n">
+      <c r="R174" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="AA173" t="inlineStr">
+      <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AO173" t="inlineStr">
+      <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP173" t="inlineStr">
+      <c r="AP174" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS173" t="inlineStr"/>
-      <c r="AT173" t="n">
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
         <v>0</v>
       </c>
-      <c r="AV173" t="inlineStr">
+      <c r="AV174" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW173" t="inlineStr">
+      <c r="AW174" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX173" t="inlineStr">
+      <c r="AX174" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr">
+      <c r="AY174" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ173" t="inlineStr">
+      <c r="AZ174" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA173" t="inlineStr">
+      <c r="BA174" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB173" t="inlineStr">
+      <c r="BB174" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC173" t="inlineStr">
+      <c r="BC174" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -25196,7 +25340,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -25206,7 +25350,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -25258,7 +25402,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3280</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="16">
